--- a/pages/shp/uploads/10-09-2025 - 10-09-2025.xlsx
+++ b/pages/shp/uploads/10-09-2025 - 10-09-2025.xlsx
@@ -1,32 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 DATA SRI\EKSPORT\Laporan Penjualan\2025\9\New folder\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" activeTab="6"/>
   </bookViews>
   <sheets>
-    <sheet name="HEADER" r:id="rId3" sheetId="1"/>
-    <sheet name="ENTITAS" r:id="rId4" sheetId="2"/>
-    <sheet name="DOKUMEN" r:id="rId5" sheetId="3"/>
-    <sheet name="PENGANGKUT" r:id="rId6" sheetId="4"/>
-    <sheet name="KEMASAN" r:id="rId7" sheetId="5"/>
-    <sheet name="KONTAINER" r:id="rId8" sheetId="6"/>
-    <sheet name="BARANG" r:id="rId9" sheetId="7"/>
-    <sheet name="BARANGTARIF" r:id="rId10" sheetId="8"/>
-    <sheet name="BARANGDOKUMEN" r:id="rId11" sheetId="9"/>
-    <sheet name="BARANGENTITAS" r:id="rId12" sheetId="10"/>
-    <sheet name="BARANGSPEKKHUSUS" r:id="rId13" sheetId="11"/>
-    <sheet name="BARANGVD" r:id="rId14" sheetId="12"/>
-    <sheet name="BAHANBAKU" r:id="rId15" sheetId="13"/>
-    <sheet name="BAHANBAKUTARIF" r:id="rId16" sheetId="14"/>
-    <sheet name="BAHANBAKUDOKUMEN" r:id="rId17" sheetId="15"/>
-    <sheet name="PUNGUTAN" r:id="rId18" sheetId="16"/>
-    <sheet name="JAMINAN" r:id="rId19" sheetId="17"/>
-    <sheet name="BANKDEVISA" r:id="rId20" sheetId="18"/>
-    <sheet name="VERSI" r:id="rId21" sheetId="19"/>
+    <sheet name="HEADER" sheetId="1" r:id="rId1"/>
+    <sheet name="ENTITAS" sheetId="2" r:id="rId2"/>
+    <sheet name="DOKUMEN" sheetId="3" r:id="rId3"/>
+    <sheet name="PENGANGKUT" sheetId="4" r:id="rId4"/>
+    <sheet name="KEMASAN" sheetId="5" r:id="rId5"/>
+    <sheet name="KONTAINER" sheetId="6" r:id="rId6"/>
+    <sheet name="BARANG" sheetId="7" r:id="rId7"/>
+    <sheet name="BARANGTARIF" sheetId="8" r:id="rId8"/>
+    <sheet name="BARANGDOKUMEN" sheetId="9" r:id="rId9"/>
+    <sheet name="BARANGENTITAS" sheetId="10" r:id="rId10"/>
+    <sheet name="BARANGSPEKKHUSUS" sheetId="11" r:id="rId11"/>
+    <sheet name="BARANGVD" sheetId="12" r:id="rId12"/>
+    <sheet name="BAHANBAKU" sheetId="13" r:id="rId13"/>
+    <sheet name="BAHANBAKUTARIF" sheetId="14" r:id="rId14"/>
+    <sheet name="BAHANBAKUDOKUMEN" sheetId="15" r:id="rId15"/>
+    <sheet name="PUNGUTAN" sheetId="16" r:id="rId16"/>
+    <sheet name="JAMINAN" sheetId="17" r:id="rId17"/>
+    <sheet name="BANKDEVISA" sheetId="18" r:id="rId18"/>
+    <sheet name="VERSI" sheetId="19" r:id="rId19"/>
   </sheets>
-  <definedNames/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -1114,19 +1120,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd-MM-yyyy HH:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.00"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.00"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -1151,123 +1158,386 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:DA4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="69" max="69" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="78" max="78" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="79" max="79" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="83" max="83" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="84" max="84" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="85" max="85" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="86" max="86" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="87" max="87" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="88" max="88" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="89" max="89" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="90" max="90" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="91" max="91" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="92" max="92" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="93" max="93" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="94" max="94" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="95" max="95" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="96" max="96" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="97" max="97" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="98" max="98" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="99" max="99" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="100" max="100" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="101" max="101" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="102" max="102" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="103" max="103" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="104" max="104" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="105" max="105" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="61" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="92" max="93" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:105" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1584,7 +1854,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>102</v>
       </c>
@@ -1645,56 +1915,56 @@
       <c r="BJ2" t="s">
         <v>117</v>
       </c>
-      <c r="BK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP2" t="n">
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
         <v>0.12</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BQ2">
         <v>1.4</v>
       </c>
-      <c r="BR2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB2" t="n">
+      <c r="BR2">
+        <v>0</v>
+      </c>
+      <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
+        <v>0</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
+        <v>16436</v>
+      </c>
+      <c r="BY2">
+        <v>0</v>
+      </c>
+      <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CB2">
         <v>0.8</v>
       </c>
-      <c r="CC2" t="n">
+      <c r="CC2">
         <v>0.7</v>
       </c>
-      <c r="CD2" t="n">
-        <v>0.0</v>
+      <c r="CD2">
+        <v>0</v>
       </c>
       <c r="CE2" t="s">
         <v>118</v>
@@ -1723,8 +1993,8 @@
       <c r="CQ2" t="s">
         <v>115</v>
       </c>
-      <c r="CT2" t="n">
-        <v>0.0</v>
+      <c r="CT2">
+        <v>0</v>
       </c>
       <c r="CZ2" t="s">
         <v>123</v>
@@ -1733,7 +2003,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -1794,56 +2064,56 @@
       <c r="BJ3" t="s">
         <v>117</v>
       </c>
-      <c r="BK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>33056.64</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ3" t="n">
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>33056.639999999999</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
         <v>134998.6</v>
       </c>
-      <c r="BR3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB3" t="n">
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>16436</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3">
         <v>7816.61</v>
       </c>
-      <c r="CC3" t="n">
+      <c r="CC3">
         <v>6453.76</v>
       </c>
-      <c r="CD3" t="n">
-        <v>0.0</v>
+      <c r="CD3">
+        <v>0</v>
       </c>
       <c r="CE3" t="s">
         <v>118</v>
@@ -1872,8 +2142,8 @@
       <c r="CQ3" t="s">
         <v>115</v>
       </c>
-      <c r="CT3" t="n">
-        <v>0.0</v>
+      <c r="CT3">
+        <v>0</v>
       </c>
       <c r="CZ3" t="s">
         <v>123</v>
@@ -1882,7 +2152,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>132</v>
       </c>
@@ -1943,56 +2213,56 @@
       <c r="BJ4" t="s">
         <v>117</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BK4">
         <v>0.03</v>
       </c>
-      <c r="BL4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO4" t="n">
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
         <v>0.03</v>
       </c>
-      <c r="BP4" t="n">
+      <c r="BP4">
         <v>0.98</v>
       </c>
-      <c r="BQ4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB4" t="n">
+      <c r="BQ4">
+        <v>15</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>16436</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4">
         <v>0.6</v>
       </c>
-      <c r="CC4" t="n">
+      <c r="CC4">
         <v>0.5</v>
       </c>
-      <c r="CD4" t="n">
-        <v>0.0</v>
+      <c r="CD4">
+        <v>0</v>
       </c>
       <c r="CE4" t="s">
         <v>118</v>
@@ -2021,8 +2291,8 @@
       <c r="CQ4" t="s">
         <v>115</v>
       </c>
-      <c r="CT4" t="n">
-        <v>0.0</v>
+      <c r="CT4">
+        <v>0</v>
       </c>
       <c r="CZ4" t="s">
         <v>123</v>
@@ -2032,29 +2302,25 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2066,28 +2332,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2102,32 +2364,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2151,56 +2409,51 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:AO1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2326,50 +2579,46 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2447,32 +2696,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2493,31 +2738,27 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2535,36 +2776,32 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2597,28 +2834,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2632,11 +2865,11 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>102</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -2646,11 +2879,11 @@
         <v>341</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -2660,11 +2893,11 @@
         <v>341</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>132</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -2675,68 +2908,60 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>343</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="34.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="120.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="120.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2783,7 +3008,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>102</v>
       </c>
@@ -2803,7 +3028,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>102</v>
       </c>
@@ -2835,7 +3060,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2858,7 +3083,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -2878,7 +3103,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>102</v>
       </c>
@@ -2907,7 +3132,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -2930,7 +3155,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>124</v>
       </c>
@@ -2950,7 +3175,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>124</v>
       </c>
@@ -2967,7 +3192,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>124</v>
       </c>
@@ -2987,7 +3212,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -3016,7 +3241,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>132</v>
       </c>
@@ -3045,7 +3270,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>132</v>
       </c>
@@ -3065,7 +3290,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>132</v>
       </c>
@@ -3097,7 +3322,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>132</v>
       </c>
@@ -3120,7 +3345,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>132</v>
       </c>
@@ -3141,32 +3366,28 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3189,12 +3410,12 @@
         <v>184</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>102</v>
       </c>
-      <c r="B2" t="n">
-        <v>1.0</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>185</v>
@@ -3206,12 +3427,12 @@
         <v>187</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>102</v>
       </c>
-      <c r="B3" t="n">
-        <v>2.0</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>188</v>
@@ -3223,12 +3444,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>102</v>
       </c>
-      <c r="B4" t="n">
-        <v>3.0</v>
+      <c r="B4">
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>190</v>
@@ -3240,12 +3461,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
-      <c r="B5" t="n">
-        <v>4.0</v>
+      <c r="B5">
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>192</v>
@@ -3257,12 +3478,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
-      <c r="B6" t="n">
-        <v>1.0</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>185</v>
@@ -3274,12 +3495,12 @@
         <v>194</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
-      <c r="B7" t="n">
-        <v>2.0</v>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="s">
         <v>188</v>
@@ -3291,12 +3512,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>124</v>
       </c>
-      <c r="B8" t="n">
-        <v>3.0</v>
+      <c r="B8">
+        <v>3</v>
       </c>
       <c r="C8" t="s">
         <v>188</v>
@@ -3308,12 +3529,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>124</v>
       </c>
-      <c r="B9" t="n">
-        <v>4.0</v>
+      <c r="B9">
+        <v>4</v>
       </c>
       <c r="C9" t="s">
         <v>188</v>
@@ -3325,12 +3546,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>124</v>
       </c>
-      <c r="B10" t="n">
-        <v>5.0</v>
+      <c r="B10">
+        <v>5</v>
       </c>
       <c r="C10" t="s">
         <v>188</v>
@@ -3342,12 +3563,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>124</v>
       </c>
-      <c r="B11" t="n">
-        <v>6.0</v>
+      <c r="B11">
+        <v>6</v>
       </c>
       <c r="C11" t="s">
         <v>188</v>
@@ -3359,12 +3580,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>124</v>
       </c>
-      <c r="B12" t="n">
-        <v>7.0</v>
+      <c r="B12">
+        <v>7</v>
       </c>
       <c r="C12" t="s">
         <v>188</v>
@@ -3376,12 +3597,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>124</v>
       </c>
-      <c r="B13" t="n">
-        <v>8.0</v>
+      <c r="B13">
+        <v>8</v>
       </c>
       <c r="C13" t="s">
         <v>188</v>
@@ -3393,12 +3614,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>124</v>
       </c>
-      <c r="B14" t="n">
-        <v>9.0</v>
+      <c r="B14">
+        <v>9</v>
       </c>
       <c r="C14" t="s">
         <v>188</v>
@@ -3410,12 +3631,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>124</v>
       </c>
-      <c r="B15" t="n">
-        <v>10.0</v>
+      <c r="B15">
+        <v>10</v>
       </c>
       <c r="C15" t="s">
         <v>188</v>
@@ -3427,12 +3648,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
-      <c r="B16" t="n">
-        <v>11.0</v>
+      <c r="B16">
+        <v>11</v>
       </c>
       <c r="C16" t="s">
         <v>188</v>
@@ -3444,12 +3665,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>124</v>
       </c>
-      <c r="B17" t="n">
-        <v>12.0</v>
+      <c r="B17">
+        <v>12</v>
       </c>
       <c r="C17" t="s">
         <v>188</v>
@@ -3461,12 +3682,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>124</v>
       </c>
-      <c r="B18" t="n">
-        <v>13.0</v>
+      <c r="B18">
+        <v>13</v>
       </c>
       <c r="C18" t="s">
         <v>188</v>
@@ -3478,12 +3699,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>124</v>
       </c>
-      <c r="B19" t="n">
-        <v>14.0</v>
+      <c r="B19">
+        <v>14</v>
       </c>
       <c r="C19" t="s">
         <v>188</v>
@@ -3495,12 +3716,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>124</v>
       </c>
-      <c r="B20" t="n">
-        <v>15.0</v>
+      <c r="B20">
+        <v>15</v>
       </c>
       <c r="C20" t="s">
         <v>188</v>
@@ -3512,12 +3733,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>124</v>
       </c>
-      <c r="B21" t="n">
-        <v>16.0</v>
+      <c r="B21">
+        <v>16</v>
       </c>
       <c r="C21" t="s">
         <v>190</v>
@@ -3529,12 +3750,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>132</v>
       </c>
-      <c r="B22" t="n">
-        <v>1.0</v>
+      <c r="B22">
+        <v>1</v>
       </c>
       <c r="C22" t="s">
         <v>185</v>
@@ -3546,12 +3767,12 @@
         <v>187</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>132</v>
       </c>
-      <c r="B23" t="n">
-        <v>2.0</v>
+      <c r="B23">
+        <v>2</v>
       </c>
       <c r="C23" t="s">
         <v>188</v>
@@ -3563,12 +3784,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>132</v>
       </c>
-      <c r="B24" t="n">
-        <v>3.0</v>
+      <c r="B24">
+        <v>3</v>
       </c>
       <c r="C24" t="s">
         <v>190</v>
@@ -3580,12 +3801,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>132</v>
       </c>
-      <c r="B25" t="n">
-        <v>4.0</v>
+      <c r="B25">
+        <v>4</v>
       </c>
       <c r="C25" t="s">
         <v>192</v>
@@ -3598,34 +3819,30 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="26.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3654,11 +3871,11 @@
         <v>217</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>102</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -3674,11 +3891,11 @@
         <v>220</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -3694,11 +3911,11 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>132</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -3715,29 +3932,25 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3754,51 +3967,51 @@
         <v>226</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>102</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>227</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>228</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>1318</v>
       </c>
       <c r="E3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>132</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>227</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
@@ -3806,31 +4019,27 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3850,11 +4059,11 @@
         <v>233</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>124</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -3871,83 +4080,71 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:BO17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="137.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="59" max="59" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="137.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="47" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="51" max="52" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:67" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4150,11 +4347,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>102</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -4181,53 +4378,54 @@
       <c r="J2" t="s">
         <v>289</v>
       </c>
-      <c r="K2" t="n">
-        <v>700.0</v>
+      <c r="K2">
+        <v>700</v>
       </c>
       <c r="L2" t="s">
         <v>227</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="T2">
         <v>0.7</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>16436</v>
+      </c>
+      <c r="AC2">
         <v>1.4</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.0</v>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="3">
+        <f>+AC2/K2</f>
+        <v>2E-3</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
       </c>
       <c r="AS2" t="s">
         <v>290</v>
@@ -4235,18 +4433,18 @@
       <c r="AY2" t="s">
         <v>291</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>0.0</v>
+      <c r="BJ2">
+        <v>0</v>
       </c>
       <c r="BO2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
@@ -4273,53 +4471,53 @@
       <c r="J3" t="s">
         <v>289</v>
       </c>
-      <c r="K3" t="n">
-        <v>1194.0</v>
+      <c r="K3">
+        <v>1194</v>
       </c>
       <c r="L3" t="s">
         <v>228</v>
       </c>
-      <c r="M3" t="n">
-        <v>101.0</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="M3">
+        <v>101</v>
+      </c>
+      <c r="T3">
         <v>554.02</v>
       </c>
-      <c r="Z3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>16436</v>
+      </c>
+      <c r="AC3">
         <v>11163.9</v>
       </c>
-      <c r="AF3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
         <v>9.35</v>
       </c>
-      <c r="AK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.0</v>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
       </c>
       <c r="AS3" t="s">
         <v>290</v>
@@ -4327,18 +4525,18 @@
       <c r="AY3" t="s">
         <v>291</v>
       </c>
-      <c r="BJ3" t="n">
-        <v>0.0</v>
+      <c r="BJ3">
+        <v>0</v>
       </c>
       <c r="BO3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>124</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>4</v>
       </c>
       <c r="C4" t="s">
@@ -4365,53 +4563,53 @@
       <c r="J4" t="s">
         <v>289</v>
       </c>
-      <c r="K4" t="n">
-        <v>384.0</v>
+      <c r="K4">
+        <v>384</v>
       </c>
       <c r="L4" t="s">
         <v>228</v>
       </c>
-      <c r="M4" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="M4">
+        <v>35</v>
+      </c>
+      <c r="T4">
         <v>212.16</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>16436</v>
+      </c>
+      <c r="AC4">
         <v>3978.24</v>
       </c>
-      <c r="AF4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ4" t="n">
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
         <v>10.36</v>
       </c>
-      <c r="AK4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.0</v>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
       </c>
       <c r="AS4" t="s">
         <v>290</v>
@@ -4419,18 +4617,18 @@
       <c r="AY4" t="s">
         <v>291</v>
       </c>
-      <c r="BJ4" t="n">
-        <v>0.0</v>
+      <c r="BJ4">
+        <v>0</v>
       </c>
       <c r="BO4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>124</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>9</v>
       </c>
       <c r="C5" t="s">
@@ -4457,53 +4655,53 @@
       <c r="J5" t="s">
         <v>289</v>
       </c>
-      <c r="K5" t="n">
-        <v>1002.0</v>
+      <c r="K5">
+        <v>1002</v>
       </c>
       <c r="L5" t="s">
         <v>228</v>
       </c>
-      <c r="M5" t="n">
-        <v>85.0</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="M5">
+        <v>85</v>
+      </c>
+      <c r="T5">
         <v>433.28</v>
       </c>
-      <c r="Z5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>16436</v>
+      </c>
+      <c r="AC5">
         <v>9478.92</v>
       </c>
-      <c r="AF5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>9.46</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.0</v>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
       </c>
       <c r="AS5" t="s">
         <v>290</v>
@@ -4511,18 +4709,18 @@
       <c r="AY5" t="s">
         <v>291</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>0.0</v>
+      <c r="BJ5">
+        <v>0</v>
       </c>
       <c r="BO5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>124</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>10</v>
       </c>
       <c r="C6" t="s">
@@ -4549,53 +4747,53 @@
       <c r="J6" t="s">
         <v>289</v>
       </c>
-      <c r="K6" t="n">
-        <v>1394.0</v>
+      <c r="K6">
+        <v>1394</v>
       </c>
       <c r="L6" t="s">
         <v>228</v>
       </c>
-      <c r="M6" t="n">
-        <v>130.0</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="M6">
+        <v>130</v>
+      </c>
+      <c r="T6">
         <v>613.29</v>
       </c>
-      <c r="Z6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>16436</v>
+      </c>
+      <c r="AC6">
         <v>13187.24</v>
       </c>
-      <c r="AF6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>9.46</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.0</v>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
       </c>
       <c r="AS6" t="s">
         <v>290</v>
@@ -4603,18 +4801,18 @@
       <c r="AY6" t="s">
         <v>291</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>0.0</v>
+      <c r="BJ6">
+        <v>0</v>
       </c>
       <c r="BO6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>8</v>
       </c>
       <c r="C7" t="s">
@@ -4641,53 +4839,53 @@
       <c r="J7" t="s">
         <v>289</v>
       </c>
-      <c r="K7" t="n">
-        <v>1394.0</v>
+      <c r="K7">
+        <v>1394</v>
       </c>
       <c r="L7" t="s">
         <v>228</v>
       </c>
-      <c r="M7" t="n">
-        <v>130.0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>630.58</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="M7">
+        <v>130</v>
+      </c>
+      <c r="T7">
+        <v>630.58000000000004</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>16436</v>
+      </c>
+      <c r="AC7">
         <v>12964.2</v>
       </c>
-      <c r="AF7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>9.3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.0</v>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
       </c>
       <c r="AS7" t="s">
         <v>290</v>
@@ -4695,18 +4893,18 @@
       <c r="AY7" t="s">
         <v>291</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>0.0</v>
+      <c r="BJ7">
+        <v>0</v>
       </c>
       <c r="BO7" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>124</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>13</v>
       </c>
       <c r="C8" t="s">
@@ -4733,53 +4931,53 @@
       <c r="J8" t="s">
         <v>289</v>
       </c>
-      <c r="K8" t="n">
-        <v>600.0</v>
+      <c r="K8">
+        <v>600</v>
       </c>
       <c r="L8" t="s">
         <v>228</v>
       </c>
-      <c r="M8" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="M8">
+        <v>51</v>
+      </c>
+      <c r="T8">
         <v>231.99</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5610.0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ8" t="n">
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>16436</v>
+      </c>
+      <c r="AC8">
+        <v>5610</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
         <v>9.35</v>
       </c>
-      <c r="AK8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.0</v>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
       </c>
       <c r="AS8" t="s">
         <v>290</v>
@@ -4787,18 +4985,18 @@
       <c r="AY8" t="s">
         <v>291</v>
       </c>
-      <c r="BJ8" t="n">
-        <v>0.0</v>
+      <c r="BJ8">
+        <v>0</v>
       </c>
       <c r="BO8" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>124</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>3</v>
       </c>
       <c r="C9" t="s">
@@ -4825,53 +5023,53 @@
       <c r="J9" t="s">
         <v>289</v>
       </c>
-      <c r="K9" t="n">
-        <v>804.0</v>
+      <c r="K9">
+        <v>804</v>
       </c>
       <c r="L9" t="s">
         <v>228</v>
       </c>
-      <c r="M9" t="n">
-        <v>70.0</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="M9">
+        <v>70</v>
+      </c>
+      <c r="T9">
         <v>421.79</v>
       </c>
-      <c r="Z9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>16436</v>
+      </c>
+      <c r="AC9">
         <v>8329.44</v>
       </c>
-      <c r="AF9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
         <v>10.36</v>
       </c>
-      <c r="AK9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.0</v>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
       </c>
       <c r="AS9" t="s">
         <v>290</v>
@@ -4879,18 +5077,18 @@
       <c r="AY9" t="s">
         <v>291</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>0.0</v>
+      <c r="BJ9">
+        <v>0</v>
       </c>
       <c r="BO9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>124</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>11</v>
       </c>
       <c r="C10" t="s">
@@ -4917,53 +5115,53 @@
       <c r="J10" t="s">
         <v>289</v>
       </c>
-      <c r="K10" t="n">
-        <v>600.0</v>
+      <c r="K10">
+        <v>600</v>
       </c>
       <c r="L10" t="s">
         <v>228</v>
       </c>
-      <c r="M10" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="M10">
+        <v>51</v>
+      </c>
+      <c r="T10">
         <v>237.42</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5526.0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>9.21</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.0</v>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>16436</v>
+      </c>
+      <c r="AC10">
+        <v>5526</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
       </c>
       <c r="AS10" t="s">
         <v>290</v>
@@ -4971,18 +5169,18 @@
       <c r="AY10" t="s">
         <v>291</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>0.0</v>
+      <c r="BJ10">
+        <v>0</v>
       </c>
       <c r="BO10" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>124</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>7</v>
       </c>
       <c r="C11" t="s">
@@ -5009,53 +5207,53 @@
       <c r="J11" t="s">
         <v>289</v>
       </c>
-      <c r="K11" t="n">
-        <v>1002.0</v>
+      <c r="K11">
+        <v>1002</v>
       </c>
       <c r="L11" t="s">
         <v>228</v>
       </c>
-      <c r="M11" t="n">
-        <v>85.0</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="M11">
+        <v>85</v>
+      </c>
+      <c r="T11">
         <v>443.26</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>16436</v>
+      </c>
+      <c r="AC11">
         <v>9318.6</v>
       </c>
-      <c r="AF11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>9.3</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.0</v>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
       </c>
       <c r="AS11" t="s">
         <v>290</v>
@@ -5063,18 +5261,18 @@
       <c r="AY11" t="s">
         <v>291</v>
       </c>
-      <c r="BJ11" t="n">
-        <v>0.0</v>
+      <c r="BJ11">
+        <v>0</v>
       </c>
       <c r="BO11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>124</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>6</v>
       </c>
       <c r="C12" t="s">
@@ -5101,53 +5299,53 @@
       <c r="J12" t="s">
         <v>289</v>
       </c>
-      <c r="K12" t="n">
-        <v>1394.0</v>
+      <c r="K12">
+        <v>1394</v>
       </c>
       <c r="L12" t="s">
         <v>228</v>
       </c>
-      <c r="M12" t="n">
-        <v>130.0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>650.56</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC12" t="n">
+      <c r="M12">
+        <v>130</v>
+      </c>
+      <c r="T12">
+        <v>650.55999999999995</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>16436</v>
+      </c>
+      <c r="AC12">
         <v>13033.9</v>
       </c>
-      <c r="AF12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ12" t="n">
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
         <v>9.35</v>
       </c>
-      <c r="AK12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.0</v>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
       </c>
       <c r="AS12" t="s">
         <v>290</v>
@@ -5155,18 +5353,18 @@
       <c r="AY12" t="s">
         <v>291</v>
       </c>
-      <c r="BJ12" t="n">
-        <v>0.0</v>
+      <c r="BJ12">
+        <v>0</v>
       </c>
       <c r="BO12" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>124</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>12</v>
       </c>
       <c r="C13" t="s">
@@ -5193,53 +5391,53 @@
       <c r="J13" t="s">
         <v>289</v>
       </c>
-      <c r="K13" t="n">
-        <v>1068.0</v>
+      <c r="K13">
+        <v>1068</v>
       </c>
       <c r="L13" t="s">
         <v>228</v>
       </c>
-      <c r="M13" t="n">
-        <v>113.0</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="M13">
+        <v>113</v>
+      </c>
+      <c r="T13">
         <v>444.38</v>
       </c>
-      <c r="Z13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9836.28</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>9.21</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0.0</v>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>16436</v>
+      </c>
+      <c r="AC13">
+        <v>9836.2800000000007</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
       </c>
       <c r="AS13" t="s">
         <v>290</v>
@@ -5247,18 +5445,18 @@
       <c r="AY13" t="s">
         <v>291</v>
       </c>
-      <c r="BJ13" t="n">
-        <v>0.0</v>
+      <c r="BJ13">
+        <v>0</v>
       </c>
       <c r="BO13" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>124</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
@@ -5285,53 +5483,53 @@
       <c r="J14" t="s">
         <v>289</v>
       </c>
-      <c r="K14" t="n">
-        <v>1310.0</v>
+      <c r="K14">
+        <v>1310</v>
       </c>
       <c r="L14" t="s">
         <v>228</v>
       </c>
-      <c r="M14" t="n">
-        <v>123.0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>605.94</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="M14">
+        <v>123</v>
+      </c>
+      <c r="T14">
+        <v>605.94000000000005</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>16436</v>
+      </c>
+      <c r="AC14">
         <v>11816.2</v>
       </c>
-      <c r="AF14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ14" t="n">
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
         <v>9.02</v>
       </c>
-      <c r="AK14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0.0</v>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
       </c>
       <c r="AS14" t="s">
         <v>290</v>
@@ -5339,18 +5537,18 @@
       <c r="AY14" t="s">
         <v>291</v>
       </c>
-      <c r="BJ14" t="n">
-        <v>0.0</v>
+      <c r="BJ14">
+        <v>0</v>
       </c>
       <c r="BO14" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>124</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>14</v>
       </c>
       <c r="C15" t="s">
@@ -5377,53 +5575,53 @@
       <c r="J15" t="s">
         <v>289</v>
       </c>
-      <c r="K15" t="n">
-        <v>1068.0</v>
+      <c r="K15">
+        <v>1068</v>
       </c>
       <c r="L15" t="s">
         <v>228</v>
       </c>
-      <c r="M15" t="n">
-        <v>113.0</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="M15">
+        <v>113</v>
+      </c>
+      <c r="T15">
         <v>425.01</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9985.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>16436</v>
+      </c>
+      <c r="AC15">
+        <v>9985.7999999999993</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
         <v>9.35</v>
       </c>
-      <c r="AK15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0.0</v>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
       </c>
       <c r="AS15" t="s">
         <v>290</v>
@@ -5431,18 +5629,18 @@
       <c r="AY15" t="s">
         <v>291</v>
       </c>
-      <c r="BJ15" t="n">
-        <v>0.0</v>
+      <c r="BJ15">
+        <v>0</v>
       </c>
       <c r="BO15" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
@@ -5469,53 +5667,53 @@
       <c r="J16" t="s">
         <v>289</v>
       </c>
-      <c r="K16" t="n">
-        <v>1194.0</v>
+      <c r="K16">
+        <v>1194</v>
       </c>
       <c r="L16" t="s">
         <v>228</v>
       </c>
-      <c r="M16" t="n">
-        <v>101.0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>550.08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="M16">
+        <v>101</v>
+      </c>
+      <c r="T16">
+        <v>550.08000000000004</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>16436</v>
+      </c>
+      <c r="AC16">
         <v>10769.88</v>
       </c>
-      <c r="AF16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ16" t="n">
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
         <v>9.02</v>
       </c>
-      <c r="AK16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0.0</v>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
       </c>
       <c r="AS16" t="s">
         <v>290</v>
@@ -5523,18 +5721,18 @@
       <c r="AY16" t="s">
         <v>291</v>
       </c>
-      <c r="BJ16" t="n">
-        <v>0.0</v>
+      <c r="BJ16">
+        <v>0</v>
       </c>
       <c r="BO16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>132</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
@@ -5561,53 +5759,53 @@
       <c r="J17" t="s">
         <v>289</v>
       </c>
-      <c r="K17" t="n">
-        <v>15.0</v>
+      <c r="K17">
+        <v>15</v>
       </c>
       <c r="L17" t="s">
         <v>227</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="T17">
         <v>0.5</v>
       </c>
-      <c r="Z17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>16436.0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0.0</v>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>16436</v>
+      </c>
+      <c r="AC17">
+        <v>15</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>1</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
       </c>
       <c r="AS17" t="s">
         <v>290</v>
@@ -5615,52 +5813,48 @@
       <c r="AY17" t="s">
         <v>291</v>
       </c>
-      <c r="BJ17" t="n">
-        <v>0.0</v>
+      <c r="BJ17">
+        <v>0</v>
       </c>
       <c r="BO17" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5720,30 +5914,26 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5758,11 +5948,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait"/>
 </worksheet>
 </file>